--- a/outputs/plan/план_продаж_сезон_окт_дек_2026_Коротич.xlsx
+++ b/outputs/plan/план_продаж_сезон_окт_дек_2026_Коротич.xlsx
@@ -9,8 +9,8 @@
   <sheets>
     <sheet name="ДАШБОРД" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Косметика сезон" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Деды Морозы" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Электроника" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Электроника" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Деды Морозы" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -82,8 +82,12 @@
       <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -145,6 +149,11 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -172,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -212,6 +221,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -655,20 +669,20 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>ДЕДЫ МОРОЗЫ</t>
+          <t>ДЕДЫ МОРОЗЫ (склад+контейнер)</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>8246</v>
+        <v>43543</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>8246</v>
+        <v>43543</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>2886100</v>
+        <v>70844461</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>15240050</v>
       </c>
     </row>
     <row r="7">
@@ -722,7 +736,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Сезонность 2025: окт 17,9к → ноя 26,9к → дек 55,1к шт. Дефицит (столбец Закуп) — заказать заранее под декабрьский пик.</t>
+          <t>Сезонность 2025: окт 17,9к → ноя 26,9к → дек 55,1к. Деды Морозы: склад 30 852 (сейчас) + контейнер 12 691 (к декабрю) = 43 543 шт.</t>
         </is>
       </c>
     </row>
@@ -6410,613 +6424,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>ДЕДЫ МОРОЗЫ — СЕЗОН ОКТ-ДЕК (отдельно)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Прибыль 350 ₽/шт. Весь остаток WB надо продать к НГ (пик дек). Цену 10 000 ₽ снизить до рыночной.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="25" t="inlineStr">
-        <is>
-          <t>Артикул ВБ</t>
-        </is>
-      </c>
-      <c r="B4" s="25" t="inlineStr">
-        <is>
-          <t>Себес ₽(+ФФ)</t>
-        </is>
-      </c>
-      <c r="C4" s="25" t="inlineStr">
-        <is>
-          <t>Логистика ₽</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="inlineStr">
-        <is>
-          <t>Остаток WB</t>
-        </is>
-      </c>
-      <c r="E4" s="25" t="inlineStr">
-        <is>
-          <t>Цена до СПП ₽</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="inlineStr">
-        <is>
-          <t>Цена с СПП ₽</t>
-        </is>
-      </c>
-      <c r="G4" s="25" t="inlineStr">
-        <is>
-          <t>Маржа ₽/ед</t>
-        </is>
-      </c>
-      <c r="H4" s="25" t="inlineStr">
-        <is>
-          <t>ПЛАН сезон шт</t>
-        </is>
-      </c>
-      <c r="I4" s="25" t="inlineStr">
-        <is>
-          <t>Прибыль сезон ₽</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="n">
-        <v>48905926</v>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>352</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>279</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>496</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>2058</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>1342</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="H5" s="14" t="n">
-        <v>496</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>173600</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="n">
-        <v>48906308</v>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>352</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>279</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>2058</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>1342</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="H6" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>175000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="n">
-        <v>48906952</v>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>374</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>279</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>2105</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>1373</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="H7" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>175000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="n">
-        <v>48908708</v>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>352</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>279</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>2058</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>1342</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="H8" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>175000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="n">
-        <v>103431353</v>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>352</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>279</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>2058</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>1342</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="H9" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>175000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="n">
-        <v>103431810</v>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>352</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>279</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>2058</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>1342</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>175000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>103441912</v>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>352</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>279</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>2058</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>1342</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>175000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>104590122</v>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>352</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>279</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>2058</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>1342</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="H12" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>175000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>555213580</v>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>567</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>428</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>2821</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>1839</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="H13" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>175000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="n">
-        <v>190314011</v>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>369</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>215</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>1958</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>1277</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="H14" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>175000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="n">
-        <v>190314349</v>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>364</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>194</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>1904</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>1241</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="H15" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>175000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="n">
-        <v>555208894</v>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>567</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>596</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>3172</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>2068</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="H16" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>175000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="n">
-        <v>555134309</v>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>512</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>309</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>2457</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>1602</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>175000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="n">
-        <v>555135716</v>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>567</v>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>596</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>3172</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>2068</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="H18" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>175000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="n">
-        <v>555151552</v>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>901</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>885</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>4479</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>2921</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="H19" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>87500</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="n">
-        <v>555204573</v>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>512</v>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>430</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>2710</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>1767</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="H20" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>175000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="n">
-        <v>555212357</v>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>512</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>309</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>2457</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>1602</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="H21" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="I21" s="5" t="n">
-        <v>175000</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="26" t="inlineStr">
-        <is>
-          <t>ИТОГО ДЕДЫ МОРОЗЫ</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="n"/>
-      <c r="C22" s="23" t="n"/>
-      <c r="D22" s="27" t="n">
-        <v>8246</v>
-      </c>
-      <c r="E22" s="23" t="n"/>
-      <c r="F22" s="23" t="n"/>
-      <c r="G22" s="23" t="n"/>
-      <c r="H22" s="27" t="n">
-        <v>8246</v>
-      </c>
-      <c r="I22" s="27" t="n">
-        <v>2886100</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>Остаток WB 8,246 шт (+ ~43 000 склад/контейнер к сезону). Весь остаток WB за сезон → 2.89 млн ₽. Со складом/контейнером потенциал ~17.9 млн ₽.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7172,4 +6579,1216 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>ДЕДЫ МОРОЗЫ — РЕАЛЬНЫЕ ОСТАТКИ (склад + контейнер)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Прибыль 350 ₽/шт. Склад продаём сейчас, контейнер (40HQ) придёт к декабрю. Цель — распродать всё к НГ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>Артикул/код</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>Себес ₽</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t>Остаток шт</t>
+        </is>
+      </c>
+      <c r="E4" s="33" t="inlineStr">
+        <is>
+          <t>Цена до СПП ₽</t>
+        </is>
+      </c>
+      <c r="F4" s="33" t="inlineStr">
+        <is>
+          <t>Цена с СПП ₽</t>
+        </is>
+      </c>
+      <c r="G4" s="33" t="inlineStr">
+        <is>
+          <t>Маржа ₽/ед</t>
+        </is>
+      </c>
+      <c r="H4" s="33" t="inlineStr">
+        <is>
+          <t>Прибыль ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>▶ НА СКЛАДЕ (сейчас)</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="n"/>
+      <c r="C5" s="35" t="n"/>
+      <c r="D5" s="35" t="n"/>
+      <c r="E5" s="35" t="n"/>
+      <c r="F5" s="35" t="n"/>
+      <c r="G5" s="35" t="n"/>
+      <c r="H5" s="35" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>48905926</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Дед Мороз (№1) красный с подарком за спиной</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2579</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1342</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>902650</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>103431810</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Дед Мороз (№10) серый</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1444</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1342</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>505400</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>104590122</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Дед Мороз (№11) в клетку</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>5430</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1342</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1900500</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>555134309</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Дед Мороз (№11) 45см клетка</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>452</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1920</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2711</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1767</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>672000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>555135716</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Дед Мороз (№11) 50см клетка</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>507</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2824</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1842</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>555169767</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Дед Мороз (№11) 85см клетка</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1157</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>5143</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>3353</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>103441912</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Дед Мороз (№12) белый лыжи белые боты</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3904</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1342</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>1366400</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>103442522</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Дед Мороз (№13) белый лыжи черные боты</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>996</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1342</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>348600</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>48906308</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Дед Мороз (№3) красный с мишкой</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3506</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1342</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>1227100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>555204573</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Дед Мороз (№3) 45см с мишкой</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>452</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1421</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2711</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1767</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>497350</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>555208894</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Дед Мороз (№3) 50см с мишкой</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>507</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2824</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1842</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>48906952</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Дед Мороз (№5) красный с подарком в руке</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>314</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>4431</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>2106</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1373</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>1550850</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>555212357</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Дед Мороз (№5) 45см с подарком</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>452</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1188</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2711</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1767</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>415800</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>555213580</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Дед Мороз (№5) 50см с подарком</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>507</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>2824</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>1842</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>48908708</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Дед Мороз (№6) блестящий</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>1519</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>1342</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>531650</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>103431353</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Дед Мороз (№9) красный рябь</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1290</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>1342</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>451500</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>190314124</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>СГ-Белая с узорами</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>304</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>717</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>2084</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>1359</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>250950</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>190314349</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>СГ-Красная</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>304</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>212</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>2084</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>1359</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>74200</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Итого склад</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="17" t="n">
+        <v>30852</v>
+      </c>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="16" t="n"/>
+      <c r="H24" s="17" t="n">
+        <v>10798200</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>▶ КОНТЕЙНЕР 40HQ в пути (к декабрю)</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
+      <c r="G26" s="13" t="n"/>
+      <c r="H26" s="13" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>дм-3</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>35CM</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>5070</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>2060</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>1343</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>1774500</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>дм-3B</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>50CM</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>507</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>672</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>2825</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>1842</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>235200</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>дм-3C</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>65CM</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>841</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>3882</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>2531</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>54600</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>дм-7</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>35CM</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>930</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>2060</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>1343</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>325500</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>дм-5</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>35CM</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>2060</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>1343</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>420000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>дм-5B</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>50CM</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>507</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>444</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>2825</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>1842</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>155400</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>дм-8B</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>50CM</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>507</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>576</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>2825</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>1842</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>201600</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>дм-2</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>35CM</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>990</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>2060</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>1343</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>346500</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>дм-10</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>35CM</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>930</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>2060</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>1343</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>325500</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>дм-15</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>35CM</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>2060</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>1343</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>73500</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>СГ-1</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>СГ-Белая с узорами</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>304</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>780</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>2085</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>1359</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>273000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>СГ-2</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>СГ-Красная</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>304</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>510</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>2085</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>1359</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>178500</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>Объём, м³</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>2060</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>1343</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>18200</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Вес брутто, т</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>2060</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>1343</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>Вместимость 40HQ, м³ (ориент.)</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>2060</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>1343</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>26600</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>Загрузка по объёму, %</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>2060</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>1343</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>23800</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>Свободно, м³</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>2060</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>1343</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>Итого контейнер</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="n"/>
+      <c r="C44" s="16" t="n"/>
+      <c r="D44" s="17" t="n">
+        <v>12691</v>
+      </c>
+      <c r="E44" s="16" t="n"/>
+      <c r="F44" s="16" t="n"/>
+      <c r="G44" s="16" t="n"/>
+      <c r="H44" s="17" t="n">
+        <v>4441850</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ДЕДЫ МОРОЗЫ</t>
+        </is>
+      </c>
+      <c r="B46" s="23" t="n"/>
+      <c r="C46" s="23" t="n"/>
+      <c r="D46" s="7" t="n">
+        <v>43543</v>
+      </c>
+      <c r="E46" s="23" t="n"/>
+      <c r="F46" s="23" t="n"/>
+      <c r="G46" s="23" t="n"/>
+      <c r="H46" s="7" t="n">
+        <v>15240050</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>